--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3EB011-3559-495C-9D2B-AC0DA9379B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75164C8-5278-4FBD-9F39-3079EDC3C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="209">
   <si>
     <t>제조사</t>
   </si>
@@ -67,9 +67,6 @@
     <t>20~23년</t>
   </si>
   <si>
-    <t>카니발 4세대</t>
-  </si>
-  <si>
     <t>18~20년</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>더 뉴 쏘렌토 4세대</t>
   </si>
   <si>
-    <t>쏘렌토 4세대</t>
-  </si>
-  <si>
     <t>17~20년</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
   </si>
   <si>
     <t>06~09년</t>
-  </si>
-  <si>
-    <t>뉴쏘렌토</t>
   </si>
   <si>
     <t>K5</t>
@@ -718,6 +709,164 @@
   </si>
   <si>
     <t>DF60R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1~24년</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>K8 3.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>K8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 2.5</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGM80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>쏘렌토</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>MQ4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">쏘렌토MQ4 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>카니발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>A4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">카니발 KA4 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">카니발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KA4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구형 쏘렌토</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1080,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1130,13 +1279,13 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -1156,13 +1305,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -1182,13 +1331,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -1208,13 +1357,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
+        <v>162</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -1234,13 +1383,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -1260,13 +1409,13 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
+        <v>163</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -1283,16 +1432,16 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -1309,16 +1458,16 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -1335,19 +1484,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
@@ -1361,16 +1510,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -1387,16 +1536,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -1413,16 +1562,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -1439,16 +1588,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -1465,16 +1614,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -1491,16 +1640,16 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -1514,19 +1663,19 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -1540,19 +1689,19 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -1566,19 +1715,19 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -1592,19 +1741,19 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
+        <v>158</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -1618,19 +1767,19 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1644,19 +1793,19 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E22" t="s">
-        <v>29</v>
+        <v>157</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G22" t="s">
         <v>12</v>
@@ -1670,19 +1819,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -1696,19 +1845,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -1722,19 +1871,19 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1748,19 +1897,19 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -1774,19 +1923,19 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -1800,19 +1949,19 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1826,19 +1975,19 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -1852,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -1878,19 +2027,19 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" t="s">
-        <v>39</v>
+        <v>158</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G31" t="s">
         <v>12</v>
@@ -1904,19 +2053,19 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" t="s">
-        <v>39</v>
+        <v>157</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -1930,22 +2079,22 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -1956,19 +2105,19 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G34" t="s">
         <v>12</v>
@@ -1982,22 +2131,22 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
         <v>40</v>
       </c>
-      <c r="C35" t="s">
-        <v>43</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2008,19 +2157,19 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
         <v>40</v>
       </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -2034,19 +2183,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
         <v>40</v>
       </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -2060,22 +2209,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2086,19 +2235,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -2112,19 +2261,19 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G40" t="s">
         <v>12</v>
@@ -2138,19 +2287,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -2164,19 +2313,19 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -2190,19 +2339,19 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -2216,19 +2365,19 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -2242,19 +2391,19 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -2268,19 +2417,19 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E46" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -2294,19 +2443,19 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2320,19 +2469,19 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -2346,19 +2495,19 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" t="s">
+        <v>37</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E49" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -2372,19 +2521,19 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -2398,19 +2547,19 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -2424,19 +2573,19 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -2450,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2476,19 +2625,19 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" t="s">
         <v>57</v>
       </c>
-      <c r="C54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" t="s">
-        <v>59</v>
-      </c>
-      <c r="E54" t="s">
-        <v>60</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -2502,19 +2651,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -2528,19 +2677,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E56" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -2554,19 +2703,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2580,19 +2729,19 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -2606,19 +2755,19 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G59" t="s">
         <v>12</v>
@@ -2632,19 +2781,19 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2658,19 +2807,19 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" t="s">
         <v>66</v>
       </c>
-      <c r="C61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E61" t="s">
-        <v>69</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -2684,22 +2833,22 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E62" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2710,19 +2859,19 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E63" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G63" t="s">
         <v>12</v>
@@ -2736,19 +2885,19 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
         <v>12</v>
@@ -2762,19 +2911,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G65" t="s">
         <v>12</v>
@@ -2788,22 +2937,22 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E66" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -2814,19 +2963,19 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
         <v>12</v>
@@ -2840,22 +2989,22 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -2866,19 +3015,19 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -2892,19 +3041,19 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G70" t="s">
         <v>12</v>
@@ -2918,19 +3067,19 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E71" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G71" t="s">
         <v>12</v>
@@ -2944,19 +3093,19 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C72" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G72" t="s">
         <v>12</v>
@@ -2970,19 +3119,19 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E73" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G73" t="s">
         <v>12</v>
@@ -2996,19 +3145,19 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E74" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
@@ -3022,19 +3171,19 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -3048,19 +3197,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G76" t="s">
         <v>12</v>
@@ -3074,19 +3223,19 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E77" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G77" t="s">
         <v>12</v>
@@ -3100,19 +3249,19 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E78" t="s">
         <v>81</v>
       </c>
-      <c r="C78" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E78" t="s">
-        <v>84</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G78" t="s">
         <v>12</v>
@@ -3126,19 +3275,19 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" t="s">
         <v>81</v>
       </c>
-      <c r="C79" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E79" t="s">
-        <v>84</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G79" t="s">
         <v>12</v>
@@ -3152,19 +3301,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E80" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G80" t="s">
         <v>12</v>
@@ -3178,19 +3327,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E81" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -3204,22 +3353,22 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D82" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E82" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3230,19 +3379,19 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E83" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G83" t="s">
         <v>12</v>
@@ -3256,22 +3405,22 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E84" t="s">
         <v>88</v>
       </c>
-      <c r="C84" t="s">
-        <v>49</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E84" t="s">
-        <v>91</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3282,19 +3431,19 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E85" t="s">
         <v>88</v>
       </c>
-      <c r="C85" t="s">
-        <v>49</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" t="s">
-        <v>91</v>
-      </c>
       <c r="F85" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G85" t="s">
         <v>12</v>
@@ -3308,22 +3457,22 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3334,22 +3483,22 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3360,19 +3509,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C88" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E88" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G88" t="s">
         <v>12</v>
@@ -3386,19 +3535,19 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E89" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G89" t="s">
         <v>12</v>
@@ -3412,19 +3561,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E90" t="s">
+        <v>94</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E90" t="s">
-        <v>97</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
@@ -3438,19 +3587,19 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C91" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E91" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G91" t="s">
         <v>12</v>
@@ -3464,19 +3613,19 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
+        <v>92</v>
+      </c>
+      <c r="C92" t="s">
+        <v>93</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E92" t="s">
         <v>95</v>
       </c>
-      <c r="C92" t="s">
-        <v>96</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E92" t="s">
-        <v>98</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G92" t="s">
         <v>12</v>
@@ -3490,19 +3639,19 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E93" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G93" t="s">
         <v>12</v>
@@ -3516,22 +3665,22 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E94" t="s">
-        <v>100</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3542,19 +3691,19 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G95" t="s">
         <v>12</v>
@@ -3568,19 +3717,19 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G96" t="s">
         <v>12</v>
@@ -3594,19 +3743,19 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E97" t="s">
+        <v>100</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E97" t="s">
-        <v>103</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G97" t="s">
         <v>12</v>
@@ -3620,19 +3769,19 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E98" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G98" t="s">
         <v>12</v>
@@ -3646,19 +3795,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G99" t="s">
         <v>12</v>
@@ -3672,19 +3821,19 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E100" t="s">
+        <v>103</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E100" t="s">
-        <v>106</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G100" t="s">
         <v>12</v>
@@ -3698,19 +3847,19 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E101" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G101" t="s">
         <v>12</v>
@@ -3724,19 +3873,19 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E102" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G102" t="s">
         <v>12</v>
@@ -3750,19 +3899,19 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C103" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E103" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G103" t="s">
         <v>12</v>
@@ -3776,19 +3925,19 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E104" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G104" t="s">
         <v>12</v>
@@ -3802,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E105" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G105" t="s">
         <v>12</v>
@@ -3824,29 +3973,26 @@
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" t="s">
-        <v>8</v>
-      </c>
-      <c r="B106" t="s">
-        <v>108</v>
-      </c>
-      <c r="C106" t="s">
-        <v>72</v>
+      <c r="A106" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E106" t="s">
-        <v>108</v>
+        <v>198</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G106" t="s">
-        <v>12</v>
-      </c>
-      <c r="H106" t="s">
-        <v>13</v>
+        <v>201</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3854,19 +4000,19 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E107" t="s">
-        <v>111</v>
+        <v>158</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G107" t="s">
         <v>12</v>
@@ -3880,19 +4026,19 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G108" t="s">
         <v>12</v>
@@ -3906,19 +4052,19 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C109" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E109" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G109" t="s">
         <v>12</v>
@@ -3932,19 +4078,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E110" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G110" t="s">
         <v>12</v>
@@ -3958,19 +4104,19 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E111" t="s">
         <v>112</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G111" t="s">
         <v>12</v>
@@ -3984,19 +4130,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C112" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="E112" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="G112" t="s">
         <v>12</v>
@@ -4010,19 +4156,19 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C113" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G113" t="s">
         <v>12</v>
@@ -4036,19 +4182,19 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C114" t="s">
-        <v>72</v>
-      </c>
-      <c r="D114" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="E114" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G114" t="s">
         <v>12</v>
@@ -4062,19 +4208,19 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>10</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>196</v>
+        <v>69</v>
+      </c>
+      <c r="D115" t="s">
+        <v>58</v>
       </c>
       <c r="E115" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G115" t="s">
         <v>12</v>
@@ -4088,19 +4234,19 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="E116" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G116" t="s">
         <v>12</v>
@@ -4114,19 +4260,19 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E117" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G117" t="s">
         <v>12</v>
@@ -4140,19 +4286,19 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E118" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
         <v>12</v>
@@ -4166,19 +4312,19 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
+        <v>121</v>
+      </c>
+      <c r="C119" t="s">
         <v>124</v>
       </c>
-      <c r="C119" t="s">
-        <v>127</v>
-      </c>
       <c r="D119" s="1" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G119" t="s">
         <v>12</v>
@@ -4192,19 +4338,19 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
+        <v>121</v>
+      </c>
+      <c r="C120" t="s">
         <v>124</v>
       </c>
-      <c r="C120" t="s">
-        <v>127</v>
-      </c>
       <c r="D120" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E120" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G120" t="s">
         <v>12</v>
@@ -4218,22 +4364,22 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E121" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
+      </c>
+      <c r="G121" t="s">
+        <v>12</v>
       </c>
       <c r="H121" t="s">
         <v>13</v>
@@ -4244,22 +4390,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E122" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
@@ -4270,22 +4416,22 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E123" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H123" t="s">
         <v>13</v>
@@ -4296,22 +4442,22 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H124" t="s">
         <v>13</v>
@@ -4322,22 +4468,22 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E125" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G125" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H125" t="s">
         <v>13</v>
@@ -4348,22 +4494,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E126" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="G126" t="s">
+        <v>12</v>
       </c>
       <c r="H126" t="s">
         <v>13</v>
@@ -4374,22 +4520,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E127" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G127" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H127" t="s">
         <v>13</v>
@@ -4400,22 +4546,22 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C128" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E128" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
+      </c>
+      <c r="G128" t="s">
+        <v>12</v>
       </c>
       <c r="H128" t="s">
         <v>13</v>
@@ -4426,22 +4572,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E129" t="s">
+        <v>132</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E129" t="s">
-        <v>134</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G129" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H129" t="s">
         <v>13</v>
@@ -4452,22 +4598,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E130" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G130" t="s">
-        <v>12</v>
+        <v>161</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="H130" t="s">
         <v>13</v>
@@ -4478,19 +4624,19 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C131" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E131" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="G131" t="s">
         <v>12</v>
@@ -4504,19 +4650,19 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C132" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E132" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="G132" t="s">
         <v>12</v>
@@ -4530,19 +4676,19 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
-      </c>
-      <c r="D133" t="s">
-        <v>61</v>
+        <v>93</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="E133" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="G133" t="s">
         <v>12</v>
@@ -4556,19 +4702,19 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C134" t="s">
-        <v>99</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>161</v>
+        <v>93</v>
+      </c>
+      <c r="D134" t="s">
+        <v>58</v>
       </c>
       <c r="E134" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G134" t="s">
         <v>12</v>
@@ -4582,19 +4728,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
+        <v>136</v>
+      </c>
+      <c r="C135" t="s">
+        <v>96</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E135" t="s">
         <v>139</v>
       </c>
-      <c r="C135" t="s">
-        <v>99</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E135" t="s">
-        <v>142</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G135" t="s">
         <v>12</v>
@@ -4608,19 +4754,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
+        <v>136</v>
+      </c>
+      <c r="C136" t="s">
+        <v>96</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E136" t="s">
         <v>139</v>
       </c>
-      <c r="C136" t="s">
-        <v>94</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E136" t="s">
-        <v>143</v>
-      </c>
       <c r="F136" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G136" t="s">
         <v>12</v>
@@ -4634,19 +4780,19 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C137" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E137" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G137" t="s">
         <v>12</v>
@@ -4660,19 +4806,19 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G138" t="s">
         <v>12</v>
@@ -4686,19 +4832,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C139" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E139" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G139" t="s">
         <v>12</v>
@@ -4712,19 +4858,19 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C140" t="s">
-        <v>145</v>
-      </c>
-      <c r="D140" t="s">
-        <v>61</v>
+        <v>141</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="E140" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G140" t="s">
         <v>12</v>
@@ -4738,22 +4884,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="D141" t="s">
+        <v>58</v>
       </c>
       <c r="E141" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="G141" t="s">
+        <v>12</v>
       </c>
       <c r="H141" t="s">
         <v>13</v>
@@ -4764,22 +4910,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C142" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E142" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H142" t="s">
         <v>13</v>
@@ -4790,22 +4936,22 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C143" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E143" t="s">
+        <v>145</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E143" t="s">
-        <v>150</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G143" t="s">
-        <v>12</v>
+      <c r="G143" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H143" t="s">
         <v>13</v>
@@ -4816,19 +4962,19 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C144" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E144" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G144" t="s">
         <v>12</v>
@@ -4842,19 +4988,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C145" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D145" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E145" t="s">
+        <v>147</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E145" t="s">
-        <v>151</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G145" t="s">
         <v>12</v>
@@ -4868,19 +5014,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C146" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E146" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
@@ -4894,19 +5040,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E147" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G147" t="s">
         <v>12</v>
@@ -4920,19 +5066,19 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C148" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E148" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G148" t="s">
         <v>12</v>
@@ -4946,19 +5092,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C149" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E149" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G149" t="s">
         <v>12</v>
@@ -4972,19 +5118,19 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C150" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E150" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G150" t="s">
         <v>12</v>
@@ -4998,19 +5144,19 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C151" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E151" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G151" t="s">
         <v>12</v>
@@ -5024,22 +5170,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C152" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E152" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="G152" t="s">
+        <v>12</v>
       </c>
       <c r="H152" t="s">
         <v>13</v>
@@ -5050,22 +5196,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C153" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E153" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G153" t="s">
-        <v>12</v>
+        <v>183</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H153" t="s">
         <v>13</v>
@@ -5076,22 +5222,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C154" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E154" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="G154" t="s">
+        <v>12</v>
       </c>
       <c r="H154" t="s">
         <v>13</v>
@@ -5102,24 +5248,50 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C155" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E155" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G155" t="s">
-        <v>12</v>
+        <v>183</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H155" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>153</v>
+      </c>
+      <c r="C156" t="s">
+        <v>52</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E156" t="s">
+        <v>155</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G156" t="s">
+        <v>12</v>
+      </c>
+      <c r="H156" t="s">
         <v>13</v>
       </c>
     </row>

--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75164C8-5278-4FBD-9F39-3079EDC3C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B8E999-CE4C-4168-AE3D-806692A7D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="207">
   <si>
     <t>제조사</t>
   </si>
@@ -82,9 +82,6 @@
     <t>10~14년</t>
   </si>
   <si>
-    <t>LPG 2700cc</t>
-  </si>
-  <si>
     <t>카니발 R</t>
   </si>
   <si>
@@ -94,12 +91,6 @@
     <t>그랜드 카니발</t>
   </si>
   <si>
-    <t>가솔린 3800cc</t>
-  </si>
-  <si>
-    <t>디젤 2900cc</t>
-  </si>
-  <si>
     <t>쏘렌토</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t>더 뉴 K5 3세대</t>
   </si>
   <si>
-    <t>가솔린 1600cc</t>
-  </si>
-  <si>
     <t>19~23년</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
   </si>
   <si>
     <t>22년~현재</t>
-  </si>
-  <si>
-    <t>가솔린 1000cc</t>
   </si>
   <si>
     <t>더 뉴 기아 레이</t>
@@ -645,10 +630,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>LPG 1000cc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>D</t>
     </r>
@@ -742,29 +723,6 @@
         <charset val="129"/>
       </rPr>
       <t>1~24년</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가솔린</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>K8 3.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>K8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 2.5</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -867,6 +825,45 @@
   </si>
   <si>
     <t>구형 쏘렌토</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가솔린 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">디젤 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LPG </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 3.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">K8 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>K8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1279,13 +1276,13 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -1305,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -1331,13 +1328,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -1357,13 +1354,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -1383,13 +1380,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -1409,13 +1406,13 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -1435,13 +1432,13 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -1461,13 +1458,13 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -1487,16 +1484,16 @@
         <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
@@ -1513,13 +1510,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -1539,13 +1536,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -1565,13 +1562,13 @@
         <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -1588,16 +1585,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -1614,16 +1611,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -1640,16 +1637,16 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -1663,19 +1660,19 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -1689,19 +1686,19 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -1715,19 +1712,19 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -1741,19 +1738,19 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -1767,19 +1764,19 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1793,19 +1790,19 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G22" t="s">
         <v>12</v>
@@ -1819,19 +1816,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" t="s">
-        <v>29</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -1845,19 +1842,19 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -1871,19 +1868,19 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1897,19 +1894,19 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -1923,19 +1920,19 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -1949,19 +1946,19 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1975,19 +1972,19 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -2001,19 +1998,19 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -2027,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G31" t="s">
         <v>12</v>
@@ -2053,19 +2050,19 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -2079,22 +2076,22 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -2105,19 +2102,19 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G34" t="s">
         <v>12</v>
@@ -2131,22 +2128,22 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" t="s">
-        <v>41</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2157,19 +2154,19 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E36" t="s">
-        <v>41</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -2183,19 +2180,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -2209,22 +2206,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2235,19 +2232,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -2261,19 +2258,19 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G40" t="s">
         <v>12</v>
@@ -2287,19 +2284,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -2313,19 +2310,19 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -2339,19 +2336,19 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -2365,19 +2362,19 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -2391,19 +2388,19 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -2417,19 +2414,19 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E46" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -2443,19 +2440,19 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2469,19 +2466,19 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -2495,19 +2492,19 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -2521,19 +2518,19 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -2547,19 +2544,19 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -2573,19 +2570,19 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -2599,19 +2596,19 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2625,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -2651,19 +2648,19 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -2677,19 +2674,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="E56" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -2703,19 +2700,19 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="E57" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2729,19 +2726,19 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -2755,19 +2752,19 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E59" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G59" t="s">
         <v>12</v>
@@ -2781,19 +2778,19 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2807,19 +2804,19 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E61" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -2833,22 +2830,22 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E62" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" t="s">
-        <v>68</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2859,19 +2856,19 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E63" t="s">
         <v>63</v>
       </c>
-      <c r="C63" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E63" t="s">
-        <v>68</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G63" t="s">
         <v>12</v>
@@ -2885,19 +2882,19 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E64" t="s">
         <v>63</v>
       </c>
-      <c r="C64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E64" t="s">
-        <v>68</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G64" t="s">
         <v>12</v>
@@ -2911,19 +2908,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G65" t="s">
         <v>12</v>
@@ -2937,22 +2934,22 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E66" t="s">
+        <v>67</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E66" t="s">
-        <v>72</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -2963,19 +2960,19 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G67" t="s">
         <v>12</v>
@@ -2989,22 +2986,22 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E68" t="s">
+        <v>68</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E68" t="s">
-        <v>73</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -3015,19 +3012,19 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E69" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -3041,19 +3038,19 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E70" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G70" t="s">
         <v>12</v>
@@ -3067,19 +3064,19 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E71" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G71" t="s">
         <v>12</v>
@@ -3093,19 +3090,19 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C72" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E72" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G72" t="s">
         <v>12</v>
@@ -3119,19 +3116,19 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E73" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G73" t="s">
         <v>12</v>
@@ -3145,19 +3142,19 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
@@ -3171,19 +3168,19 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E75" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -3197,19 +3194,19 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E76" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G76" t="s">
         <v>12</v>
@@ -3223,19 +3220,19 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E77" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G77" t="s">
         <v>12</v>
@@ -3249,19 +3246,19 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C78" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E78" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G78" t="s">
         <v>12</v>
@@ -3275,19 +3272,19 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E79" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G79" t="s">
         <v>12</v>
@@ -3301,19 +3298,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" t="s">
+        <v>77</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E80" t="s">
         <v>78</v>
       </c>
-      <c r="C80" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E80" t="s">
-        <v>83</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G80" t="s">
         <v>12</v>
@@ -3327,19 +3324,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C81" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E81" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -3353,22 +3350,22 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>67</v>
-      </c>
-      <c r="D82" t="s">
-        <v>39</v>
+        <v>62</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="E82" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3379,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G83" t="s">
         <v>12</v>
@@ -3405,22 +3402,22 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E84" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3431,19 +3428,19 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G85" t="s">
         <v>12</v>
@@ -3457,22 +3454,22 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3483,22 +3480,22 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" t="s">
         <v>85</v>
       </c>
-      <c r="C87" t="s">
-        <v>90</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E87" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3509,19 +3506,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88" t="s">
         <v>85</v>
       </c>
-      <c r="C88" t="s">
-        <v>90</v>
-      </c>
       <c r="D88" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E88" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G88" t="s">
         <v>12</v>
@@ -3535,19 +3532,19 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E89" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G89" t="s">
         <v>12</v>
@@ -3561,19 +3558,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C90" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E90" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
@@ -3587,19 +3584,19 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E91" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G91" t="s">
         <v>12</v>
@@ -3613,19 +3610,19 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C92" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E92" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G92" t="s">
         <v>12</v>
@@ -3639,19 +3636,19 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E93" t="s">
         <v>92</v>
       </c>
-      <c r="C93" t="s">
-        <v>96</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E93" t="s">
-        <v>97</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G93" t="s">
         <v>12</v>
@@ -3665,22 +3662,22 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E94" t="s">
         <v>92</v>
       </c>
-      <c r="C94" t="s">
-        <v>96</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E94" t="s">
-        <v>97</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3691,19 +3688,19 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
+        <v>87</v>
+      </c>
+      <c r="C95" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" t="s">
         <v>92</v>
       </c>
-      <c r="C95" t="s">
-        <v>96</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E95" t="s">
-        <v>97</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G95" t="s">
         <v>12</v>
@@ -3717,19 +3714,19 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E96" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G96" t="s">
         <v>12</v>
@@ -3743,19 +3740,19 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E97" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G97" t="s">
         <v>12</v>
@@ -3769,19 +3766,19 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E98" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G98" t="s">
         <v>12</v>
@@ -3795,19 +3792,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C99" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E99" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G99" t="s">
         <v>12</v>
@@ -3821,19 +3818,19 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C100" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E100" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G100" t="s">
         <v>12</v>
@@ -3847,19 +3844,19 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E101" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G101" t="s">
         <v>12</v>
@@ -3873,19 +3870,19 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E102" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G102" t="s">
         <v>12</v>
@@ -3899,19 +3896,19 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E103" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G103" t="s">
         <v>12</v>
@@ -3925,19 +3922,19 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C104" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E104" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G104" t="s">
         <v>12</v>
@@ -3951,19 +3948,19 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G105" t="s">
         <v>12</v>
@@ -3974,25 +3971,25 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4000,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G107" t="s">
         <v>12</v>
@@ -4026,19 +4023,19 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E108" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G108" t="s">
         <v>12</v>
@@ -4052,19 +4049,19 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E109" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G109" t="s">
         <v>12</v>
@@ -4078,19 +4075,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E110" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G110" t="s">
         <v>12</v>
@@ -4104,19 +4101,19 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E111" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G111" t="s">
         <v>12</v>
@@ -4130,19 +4127,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G112" t="s">
         <v>12</v>
@@ -4156,19 +4153,19 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C113" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E113" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G113" t="s">
         <v>12</v>
@@ -4182,19 +4179,19 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C114" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G114" t="s">
         <v>12</v>
@@ -4208,19 +4205,19 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C115" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E115" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G115" t="s">
         <v>12</v>
@@ -4234,19 +4231,19 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C116" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E116" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G116" t="s">
         <v>12</v>
@@ -4260,19 +4257,19 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E117" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G117" t="s">
         <v>12</v>
@@ -4286,19 +4283,19 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E118" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G118" t="s">
         <v>12</v>
@@ -4312,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C119" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E119" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G119" t="s">
         <v>12</v>
@@ -4338,19 +4335,19 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C120" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E120" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G120" t="s">
         <v>12</v>
@@ -4364,19 +4361,19 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E121" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G121" t="s">
         <v>12</v>
@@ -4390,22 +4387,22 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C122" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E122" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
@@ -4416,22 +4413,22 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E123" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H123" t="s">
         <v>13</v>
@@ -4442,22 +4439,22 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E124" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H124" t="s">
         <v>13</v>
@@ -4468,22 +4465,22 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C125" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E125" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H125" t="s">
         <v>13</v>
@@ -4494,19 +4491,19 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E126" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G126" t="s">
         <v>12</v>
@@ -4520,22 +4517,22 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E127" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H127" t="s">
         <v>13</v>
@@ -4546,19 +4543,19 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E128" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G128" t="s">
         <v>12</v>
@@ -4572,22 +4569,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E129" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H129" t="s">
         <v>13</v>
@@ -4598,22 +4595,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E130" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H130" t="s">
         <v>13</v>
@@ -4624,19 +4621,19 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E131" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G131" t="s">
         <v>12</v>
@@ -4650,19 +4647,19 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C132" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E132" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G132" t="s">
         <v>12</v>
@@ -4676,19 +4673,19 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E133" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G133" t="s">
         <v>12</v>
@@ -4702,19 +4699,19 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C134" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E134" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G134" t="s">
         <v>12</v>
@@ -4728,19 +4725,19 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C135" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E135" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G135" t="s">
         <v>12</v>
@@ -4754,19 +4751,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C136" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E136" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G136" t="s">
         <v>12</v>
@@ -4780,19 +4777,19 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C137" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E137" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G137" t="s">
         <v>12</v>
@@ -4806,19 +4803,19 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C138" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E138" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G138" t="s">
         <v>12</v>
@@ -4832,19 +4829,19 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
+        <v>131</v>
+      </c>
+      <c r="C139" t="s">
         <v>136</v>
       </c>
-      <c r="C139" t="s">
-        <v>141</v>
-      </c>
       <c r="D139" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E139" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G139" t="s">
         <v>12</v>
@@ -4858,19 +4855,19 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
+        <v>131</v>
+      </c>
+      <c r="C140" t="s">
         <v>136</v>
       </c>
-      <c r="C140" t="s">
-        <v>141</v>
-      </c>
       <c r="D140" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E140" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G140" t="s">
         <v>12</v>
@@ -4884,19 +4881,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C141" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D141" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>12</v>
@@ -4910,22 +4907,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C142" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E142" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H142" t="s">
         <v>13</v>
@@ -4936,22 +4933,22 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C143" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E143" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H143" t="s">
         <v>13</v>
@@ -4962,19 +4959,19 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C144" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E144" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G144" t="s">
         <v>12</v>
@@ -4988,19 +4985,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C145" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E145" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G145" t="s">
         <v>12</v>
@@ -5014,19 +5011,19 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C146" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E146" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
@@ -5040,19 +5037,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C147" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E147" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G147" t="s">
         <v>12</v>
@@ -5066,19 +5063,19 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C148" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E148" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G148" t="s">
         <v>12</v>
@@ -5092,19 +5089,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C149" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E149" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G149" t="s">
         <v>12</v>
@@ -5118,19 +5115,19 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C150" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E150" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G150" t="s">
         <v>12</v>
@@ -5144,19 +5141,19 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C151" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E151" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G151" t="s">
         <v>12</v>
@@ -5170,19 +5167,19 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C152" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E152" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G152" t="s">
         <v>12</v>
@@ -5196,22 +5193,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
+        <v>148</v>
+      </c>
+      <c r="C153" t="s">
+        <v>77</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C153" t="s">
-        <v>82</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E153" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H153" t="s">
         <v>13</v>
@@ -5222,19 +5219,19 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E154" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G154" t="s">
         <v>12</v>
@@ -5248,22 +5245,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C155" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E155" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H155" t="s">
         <v>13</v>
@@ -5274,19 +5271,19 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C156" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E156" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G156" t="s">
         <v>12</v>
@@ -5298,5 +5295,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B8E999-CE4C-4168-AE3D-806692A7D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC31D11-9F15-4B5C-BD59-0DBB46D7470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="211">
   <si>
     <t>제조사</t>
   </si>
@@ -55,9 +55,6 @@
     <t>23년~현재</t>
   </si>
   <si>
-    <t>더 뉴 카니발 4세대</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>쏘렌토</t>
   </si>
   <si>
-    <t>더 뉴 쏘렌토 4세대</t>
-  </si>
-  <si>
     <t>17~20년</t>
   </si>
   <si>
@@ -127,18 +121,9 @@
     <t>K5</t>
   </si>
   <si>
-    <t>더 뉴 K5 3세대</t>
-  </si>
-  <si>
     <t>19~23년</t>
   </si>
   <si>
-    <t>K5 3세대</t>
-  </si>
-  <si>
-    <t>K5 하이브리드 3세대</t>
-  </si>
-  <si>
     <t>18~19년</t>
   </si>
   <si>
@@ -202,31 +187,13 @@
     <t>24년~현재</t>
   </si>
   <si>
-    <t>더 뉴 스포티지 5세대</t>
-  </si>
-  <si>
-    <t>더 뉴 스포티지 5세대 하이브리드</t>
-  </si>
-  <si>
     <t>21년~현재</t>
   </si>
   <si>
-    <t>스포티지 5세대</t>
-  </si>
-  <si>
     <t>21~24년</t>
   </si>
   <si>
-    <t>스포티지 5세대 하이브리드</t>
-  </si>
-  <si>
     <t>18~21년</t>
-  </si>
-  <si>
-    <t>스포티지 더 볼드</t>
-  </si>
-  <si>
-    <t>스포티지 4세대</t>
   </si>
   <si>
     <t>더 뉴 스포티지 R</t>
@@ -861,6 +828,258 @@
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">스포티지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">스포티지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NQ5</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">스포티지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NQ5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> 하이브리드</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">더 뉴 스포티지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NQ5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>하이브리드</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">더 뉴 스포티지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NQ5</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>스포티지Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t>4세대</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스포티지QL 더 볼드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스포티지QL 4세대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>더 뉴 쏘렌토</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>MQ4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">더 뉴 카니발 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KA4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">K5 하이브리드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DL3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">K5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">DL3 </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>K5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> DL3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">더 뉴 K5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DL3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>더 뉴 K5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> DL3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1276,19 +1495,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
+        <v>142</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1302,19 +1521,19 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
+        <v>140</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1328,19 +1547,19 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
+        <v>141</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1351,22 +1570,22 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1377,22 +1596,22 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1403,22 +1622,22 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1429,22 +1648,22 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1455,22 +1674,22 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1481,22 +1700,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1507,22 +1726,22 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1533,22 +1752,22 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1559,22 +1778,22 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1585,22 +1804,22 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1611,22 +1830,22 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1637,22 +1856,22 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1660,25 +1879,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1686,25 +1905,25 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
+        <v>140</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1712,25 +1931,25 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
+        <v>141</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1738,25 +1957,25 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1764,25 +1983,25 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1790,25 +2009,25 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1816,25 +2035,25 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1842,25 +2061,25 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
-        <v>25</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1868,25 +2087,25 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1894,25 +2113,25 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1920,25 +2139,25 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1946,25 +2165,25 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1972,25 +2191,25 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1998,25 +2217,25 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2024,25 +2243,25 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2050,25 +2269,25 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2076,25 +2295,25 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E33" t="s">
-        <v>35</v>
+        <v>146</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2102,25 +2321,25 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2128,25 +2347,25 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" t="s">
-        <v>37</v>
+        <v>146</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2154,25 +2373,25 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E36" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2180,25 +2399,25 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" t="s">
-        <v>38</v>
+        <v>140</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2206,25 +2425,25 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
         <v>34</v>
       </c>
-      <c r="C38" t="s">
-        <v>39</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2232,25 +2451,25 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
         <v>34</v>
       </c>
-      <c r="C39" t="s">
-        <v>39</v>
-      </c>
       <c r="D39" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E39" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2258,25 +2477,25 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2284,25 +2503,25 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
         <v>34</v>
       </c>
-      <c r="C41" t="s">
-        <v>39</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2310,25 +2529,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2336,25 +2555,25 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>38</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E43" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2362,25 +2581,25 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2388,25 +2607,25 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2414,25 +2633,25 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2440,25 +2659,25 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2466,25 +2685,25 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2492,25 +2711,25 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2518,25 +2737,25 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2544,25 +2763,25 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2570,25 +2789,25 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2596,25 +2815,25 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2622,25 +2841,25 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E54" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2648,25 +2867,25 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2674,25 +2893,25 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" t="s">
         <v>50</v>
       </c>
-      <c r="C56" t="s">
-        <v>55</v>
-      </c>
       <c r="D56" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2700,25 +2919,25 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2726,25 +2945,25 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2752,25 +2971,25 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" t="s">
-        <v>60</v>
+        <v>146</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2778,25 +2997,25 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E60" t="s">
-        <v>60</v>
+        <v>142</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2804,25 +3023,25 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E61" t="s">
-        <v>61</v>
+        <v>140</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2830,25 +3049,25 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" t="s">
-        <v>63</v>
+        <v>167</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2856,25 +3075,25 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" t="s">
-        <v>63</v>
+        <v>155</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2882,25 +3101,25 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E64" t="s">
-        <v>63</v>
+        <v>141</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2908,25 +3127,25 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" t="s">
-        <v>65</v>
+        <v>168</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2934,25 +3153,25 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E66" t="s">
-        <v>67</v>
+        <v>155</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2960,25 +3179,25 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E67" t="s">
-        <v>67</v>
+        <v>141</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2986,25 +3205,25 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E68" t="s">
-        <v>68</v>
+        <v>155</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3012,25 +3231,25 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E69" t="s">
-        <v>68</v>
+        <v>156</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3038,25 +3257,25 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" t="s">
+        <v>40</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" t="s">
         <v>58</v>
       </c>
-      <c r="C70" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E70" t="s">
-        <v>69</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3064,25 +3283,25 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71" t="s">
         <v>58</v>
       </c>
-      <c r="C71" t="s">
-        <v>45</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E71" t="s">
-        <v>69</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3090,25 +3309,25 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3116,25 +3335,25 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E73" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3142,25 +3361,25 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E74" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3168,25 +3387,25 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E75" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3194,25 +3413,25 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3220,25 +3439,25 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3246,25 +3465,25 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E78" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3272,25 +3491,25 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E79" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3298,25 +3517,25 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C80" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E80" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3324,25 +3543,25 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3350,25 +3569,25 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C82" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3376,25 +3595,25 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" t="s">
+        <v>71</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E83" t="s">
-        <v>82</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3402,25 +3621,25 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C84" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E84" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3428,25 +3647,25 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C85" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3454,25 +3673,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3480,25 +3699,25 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3506,25 +3725,25 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C88" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3532,25 +3751,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3558,25 +3777,25 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E90" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3584,25 +3803,25 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C91" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E91" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3610,25 +3829,25 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E92" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3636,25 +3855,25 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3662,25 +3881,25 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C94" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E94" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E94" t="s">
-        <v>92</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G94" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3688,25 +3907,25 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E95" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3714,25 +3933,25 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C96" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E96" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3740,25 +3959,25 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3766,25 +3985,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E98" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3792,25 +4011,25 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C99" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E99" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3818,25 +4037,25 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
+        <v>76</v>
+      </c>
+      <c r="C100" t="s">
+        <v>86</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E100" t="s">
         <v>87</v>
       </c>
-      <c r="C100" t="s">
-        <v>97</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E100" t="s">
-        <v>98</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3844,25 +4063,25 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
+        <v>76</v>
+      </c>
+      <c r="C101" t="s">
+        <v>86</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E101" t="s">
         <v>87</v>
       </c>
-      <c r="C101" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E101" t="s">
-        <v>98</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3870,25 +4089,25 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C102" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E102" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3896,25 +4115,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C103" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" t="s">
+        <v>90</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E103" t="s">
-        <v>101</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3922,25 +4141,25 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E104" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3948,48 +4167,48 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E105" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3997,25 +4216,25 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C107" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4023,25 +4242,25 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E108" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4049,25 +4268,25 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C109" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E109" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -4075,25 +4294,25 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C110" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E110" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4101,25 +4320,25 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E111" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4127,25 +4346,25 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E112" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4153,25 +4372,25 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E113" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4179,25 +4398,25 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C114" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E114" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -4205,25 +4424,25 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C115" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D115" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -4231,25 +4450,25 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C116" t="s">
         <v>10</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E116" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4257,25 +4476,25 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C117" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4283,25 +4502,25 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C118" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E118" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4309,25 +4528,25 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C119" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E119" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H119" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4335,25 +4554,25 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E120" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4361,25 +4580,25 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C121" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E121" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4387,25 +4606,25 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E122" t="s">
+        <v>112</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G122" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E122" t="s">
-        <v>123</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="H122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4413,25 +4632,25 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E123" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4439,25 +4658,25 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D124" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E124" t="s">
+        <v>113</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E124" t="s">
-        <v>124</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="H124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4465,25 +4684,25 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D125" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E125" t="s">
+        <v>111</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E125" t="s">
-        <v>122</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4491,25 +4710,25 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C126" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E126" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4517,25 +4736,25 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D127" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E127" t="s">
+        <v>114</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G127" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E127" t="s">
-        <v>125</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="H127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4543,25 +4762,25 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E128" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4569,25 +4788,25 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E129" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4595,25 +4814,25 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C130" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E130" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="H130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4621,25 +4840,25 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E131" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4647,25 +4866,25 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C132" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E132" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4673,25 +4892,25 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C133" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E133" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4699,25 +4918,25 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C134" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D134" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E134" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4725,25 +4944,25 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C135" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E135" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4751,25 +4970,25 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C136" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E136" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4777,25 +4996,25 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E137" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4803,25 +5022,25 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C138" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E138" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4829,25 +5048,25 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C139" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E139" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4855,25 +5074,25 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C140" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E140" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4881,25 +5100,25 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C141" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D141" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E141" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4907,25 +5126,25 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C142" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E142" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4933,25 +5152,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C143" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E143" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4959,25 +5178,25 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C144" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E144" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4985,25 +5204,25 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
+        <v>130</v>
+      </c>
+      <c r="C145" t="s">
+        <v>73</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C145" t="s">
-        <v>84</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E145" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5011,25 +5230,25 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C146" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E146" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5037,25 +5256,25 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
+        <v>130</v>
+      </c>
+      <c r="C147" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C147" t="s">
-        <v>86</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E147" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5063,25 +5282,25 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C148" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E148" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H148" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5089,25 +5308,25 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C149" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E149" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H149" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5115,25 +5334,25 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C150" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E150" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5141,25 +5360,25 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C151" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E151" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5167,25 +5386,25 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C152" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E152" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5193,25 +5412,25 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C153" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E153" t="s">
+        <v>138</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G153" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F153" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="H153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5219,25 +5438,25 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C154" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E154" t="s">
+        <v>138</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F154" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="G154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5245,25 +5464,25 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C155" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D155" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E155" t="s">
+        <v>139</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E155" t="s">
-        <v>150</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="G155" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="H155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5271,25 +5490,25 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C156" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E156" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC31D11-9F15-4B5C-BD59-0DBB46D7470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D455FAE-1C61-4F1D-910F-AB28982B80B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="207">
   <si>
     <t>제조사</t>
   </si>
@@ -617,10 +617,6 @@
   </si>
   <si>
     <t>LPG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가솔린+전기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -850,6 +846,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>5</t>
     </r>
@@ -867,50 +865,6 @@
         <charset val="129"/>
       </rPr>
       <t>NQ5</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">스포티지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>NQ5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t xml:space="preserve"> 하이브리드</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">더 뉴 스포티지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>NQ5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>하이브리드</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -946,6 +900,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>4세대</t>
     </r>
@@ -976,6 +932,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -993,21 +951,6 @@
         <charset val="129"/>
       </rPr>
       <t>KA4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">K5 하이브리드 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DL3</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1043,6 +986,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1080,6 +1025,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1445,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1498,7 +1445,7 @@
         <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>143</v>
@@ -1524,7 +1471,7 @@
         <v>140</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>144</v>
@@ -1550,7 +1497,7 @@
         <v>141</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>145</v>
@@ -1576,7 +1523,7 @@
         <v>146</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>145</v>
@@ -1602,7 +1549,7 @@
         <v>142</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>145</v>
@@ -1628,7 +1575,7 @@
         <v>147</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>145</v>
@@ -1807,7 +1754,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -1833,7 +1780,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -1859,7 +1806,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -1888,7 +1835,7 @@
         <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>153</v>
@@ -1914,7 +1861,7 @@
         <v>140</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>154</v>
@@ -1940,7 +1887,7 @@
         <v>141</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>145</v>
@@ -1966,7 +1913,7 @@
         <v>142</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>153</v>
@@ -1992,7 +1939,7 @@
         <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>154</v>
@@ -2018,7 +1965,7 @@
         <v>141</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>145</v>
@@ -2252,7 +2199,7 @@
         <v>142</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>158</v>
@@ -2278,7 +2225,7 @@
         <v>141</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>158</v>
@@ -2304,7 +2251,7 @@
         <v>146</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>159</v>
@@ -2330,7 +2277,7 @@
         <v>142</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>153</v>
@@ -2356,7 +2303,7 @@
         <v>146</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>159</v>
@@ -2382,7 +2329,7 @@
         <v>142</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>153</v>
@@ -2402,19 +2349,19 @@
         <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>206</v>
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2431,16 +2378,16 @@
         <v>34</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
       </c>
       <c r="H38" t="s">
         <v>12</v>
@@ -2457,13 +2404,13 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s">
         <v>35</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -2483,13 +2430,13 @@
         <v>34</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -2506,16 +2453,16 @@
         <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2535,13 +2482,13 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2561,13 +2508,13 @@
         <v>37</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
         <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -2587,13 +2534,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2610,16 +2557,16 @@
         <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -2639,7 +2586,7 @@
         <v>40</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
         <v>41</v>
@@ -2688,13 +2635,13 @@
         <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>149</v>
@@ -2717,7 +2664,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
         <v>32</v>
@@ -2769,7 +2716,7 @@
         <v>42</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
@@ -2792,16 +2739,16 @@
         <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2815,19 +2762,19 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="E53" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2844,13 +2791,13 @@
         <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>189</v>
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>48</v>
       </c>
       <c r="E54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>161</v>
@@ -2870,16 +2817,16 @@
         <v>45</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="E55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2896,13 +2843,13 @@
         <v>45</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>166</v>
@@ -2924,14 +2871,14 @@
       <c r="C57" t="s">
         <v>52</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>189</v>
+      <c r="D57" t="s">
+        <v>48</v>
       </c>
       <c r="E57" t="s">
         <v>45</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2945,19 +2892,19 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
-      </c>
-      <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2977,13 +2924,13 @@
         <v>54</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -3000,19 +2947,19 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G60" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H60" t="s">
         <v>12</v>
@@ -3026,16 +2973,16 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -3055,16 +3002,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
       </c>
       <c r="H62" t="s">
         <v>12</v>
@@ -3078,19 +3025,19 @@
         <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G63" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H63" t="s">
         <v>12</v>
@@ -3104,13 +3051,13 @@
         <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>145</v>
@@ -3130,19 +3077,19 @@
         <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G65" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H65" t="s">
         <v>12</v>
@@ -3156,19 +3103,19 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
       </c>
       <c r="H66" t="s">
         <v>12</v>
@@ -3182,16 +3129,16 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>202</v>
+        <v>155</v>
+      </c>
+      <c r="E67" t="s">
+        <v>58</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -3208,19 +3155,19 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>203</v>
+        <v>141</v>
+      </c>
+      <c r="E68" t="s">
+        <v>58</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
       </c>
       <c r="H68" t="s">
         <v>12</v>
@@ -3234,16 +3181,16 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>201</v>
+        <v>142</v>
+      </c>
+      <c r="E69" t="s">
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -3260,16 +3207,16 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -3286,16 +3233,16 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3312,16 +3259,16 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E72" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3335,16 +3282,16 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E73" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>169</v>
@@ -3361,19 +3308,19 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3387,19 +3334,19 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3416,16 +3363,16 @@
         <v>62</v>
       </c>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3442,13 +3389,13 @@
         <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E77" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>170</v>
@@ -3468,13 +3415,13 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E78" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>170</v>
@@ -3491,22 +3438,22 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="E79" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G79" t="s">
-        <v>11</v>
+        <v>154</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3517,19 +3464,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E80" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -3543,22 +3490,22 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G81" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3572,19 +3519,19 @@
         <v>69</v>
       </c>
       <c r="C82" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G82" s="1" t="s">
         <v>153</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -3598,19 +3545,19 @@
         <v>69</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E83" t="s">
-        <v>71</v>
+      <c r="E83" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G83" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -3624,13 +3571,13 @@
         <v>69</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E84" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>159</v>
@@ -3650,13 +3597,13 @@
         <v>69</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>153</v>
@@ -3673,22 +3620,22 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>172</v>
+        <v>146</v>
+      </c>
+      <c r="E86" t="s">
+        <v>78</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
       </c>
       <c r="H86" t="s">
         <v>12</v>
@@ -3699,22 +3646,22 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -3725,19 +3672,19 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C88" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3757,13 +3704,13 @@
         <v>77</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3780,16 +3727,16 @@
         <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3806,19 +3753,19 @@
         <v>76</v>
       </c>
       <c r="C91" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F91" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="G91" t="s">
-        <v>11</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -3832,16 +3779,16 @@
         <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3861,13 +3808,13 @@
         <v>80</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
@@ -3884,19 +3831,19 @@
         <v>76</v>
       </c>
       <c r="C94" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
       </c>
       <c r="H94" t="s">
         <v>12</v>
@@ -3910,16 +3857,16 @@
         <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E95" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
@@ -3936,13 +3883,13 @@
         <v>76</v>
       </c>
       <c r="C96" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>140</v>
       </c>
       <c r="E96" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>164</v>
@@ -3962,13 +3909,13 @@
         <v>76</v>
       </c>
       <c r="C97" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>146</v>
       </c>
       <c r="E97" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>149</v>
@@ -3988,13 +3935,13 @@
         <v>76</v>
       </c>
       <c r="C98" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E98" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>149</v>
@@ -4011,19 +3958,19 @@
         <v>8</v>
       </c>
       <c r="B99" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C99" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="E99" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
@@ -4037,19 +3984,19 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C100" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E100" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -4063,19 +4010,19 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C101" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E101" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="G101" t="s">
         <v>11</v>
@@ -4092,13 +4039,13 @@
         <v>89</v>
       </c>
       <c r="C102" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E102" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>153</v>
@@ -4111,29 +4058,26 @@
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B103" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" t="s">
-        <v>54</v>
+      <c r="A103" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E103" t="s">
-        <v>90</v>
+        <v>191</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G103" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4144,16 +4088,16 @@
         <v>89</v>
       </c>
       <c r="C104" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E104" t="s">
-        <v>91</v>
+        <v>192</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -4173,13 +4117,13 @@
         <v>56</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E105" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -4189,26 +4133,29 @@
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>180</v>
+      <c r="A106" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" t="s">
+        <v>93</v>
+      </c>
+      <c r="C106" t="s">
+        <v>55</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>194</v>
+        <v>142</v>
+      </c>
+      <c r="E106" t="s">
+        <v>94</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="G106" t="s">
+        <v>11</v>
+      </c>
+      <c r="H106" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4216,19 +4163,19 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C107" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>195</v>
+        <v>142</v>
+      </c>
+      <c r="E107" t="s">
+        <v>95</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -4242,19 +4189,19 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C108" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E108" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -4271,13 +4218,13 @@
         <v>93</v>
       </c>
       <c r="C109" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E109" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>173</v>
@@ -4294,19 +4241,19 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C110" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="E110" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4320,19 +4267,19 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C111" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="E111" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
@@ -4346,19 +4293,19 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C112" t="s">
-        <v>27</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>142</v>
+        <v>56</v>
+      </c>
+      <c r="D112" t="s">
+        <v>48</v>
       </c>
       <c r="E112" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4372,16 +4319,16 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C113" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>175</v>
       </c>
       <c r="E113" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>154</v>
@@ -4398,19 +4345,19 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4424,19 +4371,19 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
-      </c>
-      <c r="D115" t="s">
-        <v>48</v>
+        <v>106</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="E115" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
@@ -4450,19 +4397,19 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E116" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -4479,13 +4426,13 @@
         <v>105</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E117" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>149</v>
@@ -4505,13 +4452,13 @@
         <v>105</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E118" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>149</v>
@@ -4528,22 +4475,22 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E119" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G119" t="s">
-        <v>11</v>
+        <v>154</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4554,22 +4501,22 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C120" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E120" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G120" t="s">
-        <v>11</v>
+        <v>154</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4580,22 +4527,22 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C121" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E121" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G121" t="s">
-        <v>11</v>
+        <v>154</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4609,13 +4556,13 @@
         <v>111</v>
       </c>
       <c r="C122" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E122" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>154</v>
@@ -4635,19 +4582,19 @@
         <v>111</v>
       </c>
       <c r="C123" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G123" s="1" t="s">
         <v>153</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
       </c>
       <c r="H123" t="s">
         <v>12</v>
@@ -4658,16 +4605,16 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E124" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>154</v>
@@ -4684,22 +4631,22 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C125" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E125" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G125" s="1" t="s">
         <v>153</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
       </c>
       <c r="H125" t="s">
         <v>12</v>
@@ -4710,22 +4657,22 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C126" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E126" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G126" t="s">
-        <v>11</v>
+        <v>145</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="H126" t="s">
         <v>12</v>
@@ -4736,7 +4683,7 @@
         <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -4745,13 +4692,13 @@
         <v>142</v>
       </c>
       <c r="E127" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H127" t="s">
         <v>12</v>
@@ -4762,7 +4709,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -4771,10 +4718,10 @@
         <v>141</v>
       </c>
       <c r="E128" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4788,22 +4735,22 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C129" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E129" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>157</v>
+        <v>176</v>
+      </c>
+      <c r="G129" t="s">
+        <v>11</v>
       </c>
       <c r="H129" t="s">
         <v>12</v>
@@ -4814,22 +4761,22 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C130" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E130" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
+      </c>
+      <c r="G130" t="s">
+        <v>11</v>
       </c>
       <c r="H130" t="s">
         <v>12</v>
@@ -4840,19 +4787,19 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>141</v>
+        <v>77</v>
+      </c>
+      <c r="D131" t="s">
+        <v>48</v>
       </c>
       <c r="E131" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4866,19 +4813,19 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E132" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4895,16 +4842,16 @@
         <v>120</v>
       </c>
       <c r="C133" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E133" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4921,16 +4868,16 @@
         <v>120</v>
       </c>
       <c r="C134" t="s">
-        <v>77</v>
-      </c>
-      <c r="D134" t="s">
-        <v>48</v>
+        <v>75</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="E134" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -4947,16 +4894,16 @@
         <v>120</v>
       </c>
       <c r="C135" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E135" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -4973,16 +4920,16 @@
         <v>120</v>
       </c>
       <c r="C136" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E136" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -4999,16 +4946,16 @@
         <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E137" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -5025,16 +4972,16 @@
         <v>120</v>
       </c>
       <c r="C138" t="s">
-        <v>75</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
+      </c>
+      <c r="D138" t="s">
+        <v>48</v>
       </c>
       <c r="E138" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -5048,22 +4995,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C139" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E139" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G139" t="s">
-        <v>11</v>
+        <v>149</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H139" t="s">
         <v>12</v>
@@ -5074,22 +5021,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C140" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E140" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G140" t="s">
-        <v>11</v>
+      <c r="G140" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H140" t="s">
         <v>12</v>
@@ -5100,19 +5047,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C141" t="s">
-        <v>126</v>
-      </c>
-      <c r="D141" t="s">
-        <v>48</v>
+        <v>73</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="E141" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
@@ -5126,22 +5073,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C142" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E142" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G142" s="1" t="s">
-        <v>148</v>
+      <c r="G142" t="s">
+        <v>11</v>
       </c>
       <c r="H142" t="s">
         <v>12</v>
@@ -5152,22 +5099,22 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C143" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E143" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G143" s="1" t="s">
-        <v>148</v>
+      <c r="G143" t="s">
+        <v>11</v>
       </c>
       <c r="H143" t="s">
         <v>12</v>
@@ -5181,13 +5128,13 @@
         <v>130</v>
       </c>
       <c r="C144" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E144" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>149</v>
@@ -5204,19 +5151,19 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C145" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E145" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -5230,16 +5177,16 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C146" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>146</v>
       </c>
       <c r="E146" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>149</v>
@@ -5256,16 +5203,16 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C147" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E147" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>149</v>
@@ -5282,19 +5229,19 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C148" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -5311,13 +5258,13 @@
         <v>134</v>
       </c>
       <c r="C149" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E149" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>149</v>
@@ -5334,22 +5281,22 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C150" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E150" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G150" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="G150" t="s">
-        <v>11</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5360,16 +5307,16 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C151" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E151" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>149</v>
@@ -5386,22 +5333,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C152" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E152" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F152" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="G152" t="s">
-        <v>11</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5415,99 +5362,21 @@
         <v>137</v>
       </c>
       <c r="C153" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E153" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G153" s="1" t="s">
         <v>149</v>
       </c>
+      <c r="G153" t="s">
+        <v>11</v>
+      </c>
       <c r="H153" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
-      <c r="A154" t="s">
-        <v>8</v>
-      </c>
-      <c r="B154" t="s">
-        <v>137</v>
-      </c>
-      <c r="C154" t="s">
-        <v>66</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E154" t="s">
-        <v>138</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G154" t="s">
-        <v>11</v>
-      </c>
-      <c r="H154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>137</v>
-      </c>
-      <c r="C155" t="s">
-        <v>43</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E155" t="s">
-        <v>139</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H155" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>137</v>
-      </c>
-      <c r="C156" t="s">
-        <v>43</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E156" t="s">
-        <v>139</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G156" t="s">
-        <v>11</v>
-      </c>
-      <c r="H156" t="s">
         <v>12</v>
       </c>
     </row>

--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D455FAE-1C61-4F1D-910F-AB28982B80B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E103D0-7577-4D38-A568-A518241408A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="209">
   <si>
     <t>제조사</t>
   </si>
@@ -1030,6 +1030,14 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 카니발 KA4 하이브리드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 쏘렌토MQ4 하이브리드</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1471,7 +1479,7 @@
         <v>140</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>144</v>
@@ -1861,7 +1869,7 @@
         <v>140</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>154</v>

--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E103D0-7577-4D38-A568-A518241408A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E0A27C-B30A-4B8C-A72F-350229107924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="208">
   <si>
     <t>제조사</t>
   </si>
@@ -465,21 +465,6 @@
         <charset val="129"/>
       </rPr>
       <t>GM80</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>GM60</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1453,7 +1438,7 @@
         <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>143</v>
@@ -1479,10 +1464,10 @@
         <v>140</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1505,10 +1490,10 @@
         <v>141</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1528,13 +1513,13 @@
         <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1557,10 +1542,10 @@
         <v>142</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1580,13 +1565,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1612,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -1638,7 +1623,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -1664,10 +1649,10 @@
         <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
@@ -1690,7 +1675,7 @@
         <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1710,13 +1695,13 @@
         <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -1742,7 +1727,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1762,13 +1747,13 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1788,13 +1773,13 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1814,13 +1799,13 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1843,10 +1828,10 @@
         <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1869,10 +1854,10 @@
         <v>140</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1895,10 +1880,10 @@
         <v>141</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1921,10 +1906,10 @@
         <v>142</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1947,10 +1932,10 @@
         <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1973,10 +1958,10 @@
         <v>141</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -1996,13 +1981,13 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E23" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -2022,13 +2007,13 @@
         <v>23</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -2048,13 +2033,13 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
         <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -2074,13 +2059,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -2100,13 +2085,13 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -2126,13 +2111,13 @@
         <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -2152,13 +2137,13 @@
         <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -2184,7 +2169,7 @@
         <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -2207,10 +2192,10 @@
         <v>142</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -2233,10 +2218,10 @@
         <v>141</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -2256,16 +2241,16 @@
         <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -2285,10 +2270,10 @@
         <v>142</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -2308,16 +2293,16 @@
         <v>33</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -2337,10 +2322,10 @@
         <v>142</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -2360,16 +2345,16 @@
         <v>34</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>35</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2392,7 +2377,7 @@
         <v>35</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2418,7 +2403,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -2444,7 +2429,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -2464,13 +2449,13 @@
         <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2496,7 +2481,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2522,7 +2507,7 @@
         <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -2548,7 +2533,7 @@
         <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2568,13 +2553,13 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>41</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -2600,7 +2585,7 @@
         <v>41</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -2626,7 +2611,7 @@
         <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -2646,13 +2631,13 @@
         <v>42</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>32</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2678,7 +2663,7 @@
         <v>32</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -2704,7 +2689,7 @@
         <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2730,7 +2715,7 @@
         <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2756,7 +2741,7 @@
         <v>44</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2776,13 +2761,13 @@
         <v>46</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
         <v>47</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2808,7 +2793,7 @@
         <v>49</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2828,13 +2813,13 @@
         <v>50</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>51</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2854,13 +2839,13 @@
         <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
         <v>45</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2886,7 +2871,7 @@
         <v>45</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2906,13 +2891,13 @@
         <v>54</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2935,10 +2920,10 @@
         <v>142</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2958,16 +2943,16 @@
         <v>55</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F60" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H60" t="s">
         <v>12</v>
@@ -2984,13 +2969,13 @@
         <v>55</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -3013,10 +2998,10 @@
         <v>141</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -3036,16 +3021,16 @@
         <v>57</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H63" t="s">
         <v>12</v>
@@ -3065,10 +3050,10 @@
         <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -3088,16 +3073,16 @@
         <v>37</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H65" t="s">
         <v>12</v>
@@ -3114,13 +3099,13 @@
         <v>37</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -3140,13 +3125,13 @@
         <v>40</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E67" t="s">
         <v>58</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -3172,7 +3157,7 @@
         <v>58</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -3198,7 +3183,7 @@
         <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -3224,7 +3209,7 @@
         <v>59</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -3250,7 +3235,7 @@
         <v>61</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3276,7 +3261,7 @@
         <v>61</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3302,7 +3287,7 @@
         <v>63</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -3328,7 +3313,7 @@
         <v>64</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3348,13 +3333,13 @@
         <v>23</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
         <v>65</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3380,7 +3365,7 @@
         <v>65</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3406,7 +3391,7 @@
         <v>67</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -3432,7 +3417,7 @@
         <v>68</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -3452,16 +3437,16 @@
         <v>55</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E79" t="s">
         <v>70</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3484,7 +3469,7 @@
         <v>71</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -3510,10 +3495,10 @@
         <v>72</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3536,7 +3521,7 @@
         <v>72</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
@@ -3559,13 +3544,13 @@
         <v>142</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F83" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -3588,10 +3573,10 @@
         <v>69</v>
       </c>
       <c r="F84" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -3614,7 +3599,7 @@
         <v>69</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
@@ -3634,13 +3619,13 @@
         <v>77</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>78</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
@@ -3666,7 +3651,7 @@
         <v>78</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
@@ -3692,7 +3677,7 @@
         <v>78</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3718,7 +3703,7 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3738,13 +3723,13 @@
         <v>80</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
         <v>81</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3770,10 +3755,10 @@
         <v>81</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -3796,7 +3781,7 @@
         <v>81</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3822,7 +3807,7 @@
         <v>82</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
@@ -3842,13 +3827,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
         <v>84</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3874,7 +3859,7 @@
         <v>84</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
@@ -3900,7 +3885,7 @@
         <v>85</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -3920,13 +3905,13 @@
         <v>86</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
         <v>87</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
@@ -3952,7 +3937,7 @@
         <v>87</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3972,13 +3957,13 @@
         <v>54</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
         <v>90</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
@@ -4004,7 +3989,7 @@
         <v>90</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -4030,7 +4015,7 @@
         <v>91</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G101" t="s">
         <v>11</v>
@@ -4050,13 +4035,13 @@
         <v>56</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E102" t="s">
         <v>89</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -4067,25 +4052,25 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="H103" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4099,13 +4084,13 @@
         <v>56</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -4131,7 +4116,7 @@
         <v>92</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -4157,7 +4142,7 @@
         <v>94</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -4183,7 +4168,7 @@
         <v>95</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -4209,7 +4194,7 @@
         <v>96</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -4235,7 +4220,7 @@
         <v>93</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -4255,13 +4240,13 @@
         <v>97</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E110" t="s">
         <v>98</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4281,13 +4266,13 @@
         <v>54</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E111" t="s">
         <v>100</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
@@ -4313,7 +4298,7 @@
         <v>99</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4333,13 +4318,13 @@
         <v>10</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E113" t="s">
         <v>101</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4359,13 +4344,13 @@
         <v>106</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>107</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4391,7 +4376,7 @@
         <v>107</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
@@ -4411,13 +4396,13 @@
         <v>108</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E116" t="s">
         <v>109</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -4443,7 +4428,7 @@
         <v>109</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G117" t="s">
         <v>11</v>
@@ -4469,7 +4454,7 @@
         <v>109</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -4495,10 +4480,10 @@
         <v>112</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4521,10 +4506,10 @@
         <v>112</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4547,10 +4532,10 @@
         <v>113</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4573,10 +4558,10 @@
         <v>111</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H122" t="s">
         <v>12</v>
@@ -4599,7 +4584,7 @@
         <v>111</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G123" t="s">
         <v>11</v>
@@ -4625,10 +4610,10 @@
         <v>114</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H124" t="s">
         <v>12</v>
@@ -4651,7 +4636,7 @@
         <v>114</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G125" t="s">
         <v>11</v>
@@ -4677,10 +4662,10 @@
         <v>116</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H126" t="s">
         <v>12</v>
@@ -4703,10 +4688,10 @@
         <v>115</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H127" t="s">
         <v>12</v>
@@ -4729,7 +4714,7 @@
         <v>115</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4755,7 +4740,7 @@
         <v>119</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G129" t="s">
         <v>11</v>
@@ -4781,7 +4766,7 @@
         <v>121</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -4807,7 +4792,7 @@
         <v>122</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4833,7 +4818,7 @@
         <v>123</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4859,7 +4844,7 @@
         <v>123</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4885,7 +4870,7 @@
         <v>124</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -4911,7 +4896,7 @@
         <v>124</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -4937,7 +4922,7 @@
         <v>120</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -4963,7 +4948,7 @@
         <v>120</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4989,7 +4974,7 @@
         <v>127</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -5009,16 +4994,16 @@
         <v>88</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E139" t="s">
         <v>129</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H139" t="s">
         <v>12</v>
@@ -5041,10 +5026,10 @@
         <v>129</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H140" t="s">
         <v>12</v>
@@ -5061,13 +5046,13 @@
         <v>73</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E141" t="s">
         <v>131</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
@@ -5093,7 +5078,7 @@
         <v>131</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G142" t="s">
         <v>11</v>
@@ -5113,13 +5098,13 @@
         <v>75</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E143" t="s">
         <v>132</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G143" t="s">
         <v>11</v>
@@ -5145,7 +5130,7 @@
         <v>132</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -5165,13 +5150,13 @@
         <v>110</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E145" t="s">
         <v>133</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -5191,13 +5176,13 @@
         <v>125</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E146" t="s">
         <v>134</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G146" t="s">
         <v>11</v>
@@ -5223,7 +5208,7 @@
         <v>134</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
@@ -5249,7 +5234,7 @@
         <v>134</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -5275,7 +5260,7 @@
         <v>136</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G149" t="s">
         <v>11</v>
@@ -5301,10 +5286,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5327,7 +5312,7 @@
         <v>138</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G151" t="s">
         <v>11</v>
@@ -5347,16 +5332,16 @@
         <v>43</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E152" t="s">
         <v>139</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5379,7 +5364,7 @@
         <v>139</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G153" t="s">
         <v>11</v>

--- a/master-db/kia.xlsx
+++ b/master-db/kia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E0A27C-B30A-4B8C-A72F-350229107924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3590E24-4612-45A9-9EF4-889FEA5D4AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3443,10 +3443,10 @@
         <v>70</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3469,10 +3469,10 @@
         <v>71</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G80" t="s">
-        <v>11</v>
+        <v>158</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
